--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -840,12 +840,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x5</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5x4</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3x5</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -840,12 +840,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1x5</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5x4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3x5</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-28.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1235,19 +1235,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -2268,19 +2268,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S23" t="n">
